--- a/notebooks/Workflow_run_stats.xlsx
+++ b/notebooks/Workflow_run_stats.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bart_\Documents\Thesis\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bart_\Documents\git_repo\agentic_actuaries\notebooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDC45B41-F5AB-4B6D-8372-206E06CDE36B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F076C1-8D92-420B-9ED0-0D46E5FA8E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6703F7FF-40DD-4F79-B570-BA584D8FFEF8}"/>
   </bookViews>
@@ -647,7 +647,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -685,6 +685,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -2819,8 +2822,9 @@
         <v>0.94769861349936002</v>
       </c>
       <c r="Q23" s="5">
-        <v>0.58979999999999999</v>
-      </c>
+        <v>0.60980000000000001</v>
+      </c>
+      <c r="R23" s="17"/>
       <c r="V23" s="8">
         <v>8.6243675760395905E-2</v>
       </c>
@@ -2971,8 +2975,9 @@
         <v>0.94790442179645096</v>
       </c>
       <c r="Q25" s="5">
-        <v>0.56440000000000001</v>
-      </c>
+        <v>0.60440000000000005</v>
+      </c>
+      <c r="R25" s="17"/>
       <c r="V25" s="8">
         <v>8.6243675760395905E-2</v>
       </c>
@@ -3053,6 +3058,7 @@
       <c r="Q26" s="5">
         <v>0.58940000000000003</v>
       </c>
+      <c r="R26" s="17"/>
       <c r="V26" s="8">
         <v>8.6243675760395905E-2</v>
       </c>
@@ -3124,9 +3130,7 @@
       <c r="N27" s="4"/>
       <c r="O27" s="4"/>
       <c r="P27" s="4"/>
-      <c r="Q27" s="5">
-        <v>0.74529999999999996</v>
-      </c>
+      <c r="Q27" s="5"/>
       <c r="V27" s="8">
         <v>8.6243675760395905E-2</v>
       </c>
@@ -3205,8 +3209,9 @@
         <v>0.30795911186466102</v>
       </c>
       <c r="Q28" s="5">
-        <v>0.5766</v>
-      </c>
+        <v>0.58660000000000001</v>
+      </c>
+      <c r="R28" s="17"/>
       <c r="V28" s="8">
         <v>8.6243675760395905E-2</v>
       </c>
@@ -3285,8 +3290,9 @@
         <v>0.75476054142080395</v>
       </c>
       <c r="Q29" s="5">
-        <v>0.56269999999999998</v>
-      </c>
+        <v>0.5827</v>
+      </c>
+      <c r="R29" s="17"/>
       <c r="V29" s="8">
         <v>8.6243675760395905E-2</v>
       </c>
@@ -3367,6 +3373,7 @@
       <c r="Q30" s="5">
         <v>0.61670000000000003</v>
       </c>
+      <c r="R30" s="17"/>
       <c r="V30" s="8">
         <v>8.6243675760395905E-2</v>
       </c>
@@ -3447,6 +3454,7 @@
       <c r="Q31" s="5">
         <v>0.58020000000000005</v>
       </c>
+      <c r="R31" s="17"/>
       <c r="V31" s="8">
         <v>8.6243675760395905E-2</v>
       </c>

--- a/notebooks/Workflow_run_stats.xlsx
+++ b/notebooks/Workflow_run_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bart_\Documents\git_repo\agentic_actuaries\notebooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F076C1-8D92-420B-9ED0-0D46E5FA8E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E56EA4C7-1CC1-4D1B-B3F3-AE8083FF02F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6703F7FF-40DD-4F79-B570-BA584D8FFEF8}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="182">
   <si>
     <t>RunID</t>
   </si>
@@ -574,6 +574,18 @@
   </si>
   <si>
     <t>20260307_184747</t>
+  </si>
+  <si>
+    <t>Data_uncertainty</t>
+  </si>
+  <si>
+    <t>Review_uncertainty</t>
+  </si>
+  <si>
+    <t>Model_uncertainty</t>
+  </si>
+  <si>
+    <t>Explanation_uncertainty</t>
   </si>
 </sst>
 </file>
@@ -647,7 +659,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -687,6 +699,9 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1099,16 +1114,16 @@
         <v>28</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>78</v>
+        <v>178</v>
       </c>
       <c r="S1" s="7" t="s">
-        <v>79</v>
+        <v>179</v>
       </c>
       <c r="T1" s="7" t="s">
-        <v>80</v>
+        <v>180</v>
       </c>
       <c r="U1" s="7" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>95</v>
@@ -1189,6 +1204,18 @@
       </c>
       <c r="Q2" s="5">
         <v>0.7006</v>
+      </c>
+      <c r="R2" s="17">
+        <v>0.91610000000000003</v>
+      </c>
+      <c r="S2" s="5">
+        <v>0.89529999999999998</v>
+      </c>
+      <c r="T2" s="18">
+        <v>0.91949999999999998</v>
+      </c>
+      <c r="U2" s="5">
+        <v>0.87790000000000001</v>
       </c>
       <c r="V2" s="8">
         <v>8.6243675760395905E-2</v>
@@ -1270,6 +1297,18 @@
       <c r="Q3" s="5">
         <v>0.70789999999999997</v>
       </c>
+      <c r="R3" s="17">
+        <v>0.89100000000000001</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0.93300000000000005</v>
+      </c>
+      <c r="T3" s="5">
+        <v>0.88949999999999996</v>
+      </c>
+      <c r="U3" s="5">
+        <v>0.86729999999999996</v>
+      </c>
       <c r="V3" s="8">
         <v>8.6243675760395905E-2</v>
       </c>
@@ -1350,6 +1389,18 @@
       <c r="Q4" s="5">
         <v>0.70240000000000002</v>
       </c>
+      <c r="R4" s="17">
+        <v>0.90149999999999997</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0.91779999999999995</v>
+      </c>
+      <c r="T4" s="5">
+        <v>0.90329999999999999</v>
+      </c>
+      <c r="U4" s="5">
+        <v>0.8831</v>
+      </c>
       <c r="V4" s="8">
         <v>8.6243675760395905E-2</v>
       </c>
@@ -1510,6 +1561,18 @@
       <c r="Q6" s="5">
         <v>0.70850000000000002</v>
       </c>
+      <c r="R6" s="17">
+        <v>0.92090000000000005</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0.9012</v>
+      </c>
+      <c r="T6" s="5">
+        <v>0.9022</v>
+      </c>
+      <c r="U6" s="5">
+        <v>0.90339999999999998</v>
+      </c>
       <c r="V6" s="8">
         <v>8.6243675760395905E-2</v>
       </c>
@@ -1589,6 +1652,18 @@
       </c>
       <c r="Q7" s="5">
         <v>0.75949999999999995</v>
+      </c>
+      <c r="R7" s="17">
+        <v>0.97160000000000002</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0.89790000000000003</v>
+      </c>
+      <c r="T7" s="5">
+        <v>0.94730000000000003</v>
+      </c>
+      <c r="U7" s="5">
+        <v>0.90069999999999995</v>
       </c>
       <c r="V7" s="8">
         <v>8.6243675760395905E-2</v>
@@ -1736,6 +1811,18 @@
       <c r="Q9" s="5">
         <v>0.70289999999999997</v>
       </c>
+      <c r="R9" s="17">
+        <v>0.92630000000000001</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0.89190000000000003</v>
+      </c>
+      <c r="T9" s="5">
+        <v>0.90610000000000002</v>
+      </c>
+      <c r="U9" s="5">
+        <v>0.87970000000000004</v>
+      </c>
       <c r="V9" s="8">
         <v>8.6243675760395905E-2</v>
       </c>
@@ -1815,6 +1902,18 @@
       </c>
       <c r="Q10" s="5">
         <v>0.69440000000000002</v>
+      </c>
+      <c r="R10" s="17">
+        <v>0.93079999999999996</v>
+      </c>
+      <c r="S10" s="5">
+        <v>0.92290000000000005</v>
+      </c>
+      <c r="T10" s="5">
+        <v>0.89970000000000006</v>
+      </c>
+      <c r="U10" s="5">
+        <v>0.86150000000000004</v>
       </c>
       <c r="V10" s="8">
         <v>8.6243675760395905E-2</v>
@@ -1961,6 +2060,18 @@
       </c>
       <c r="Q12" s="5">
         <v>0.55130000000000001</v>
+      </c>
+      <c r="R12" s="17">
+        <v>0.85399999999999998</v>
+      </c>
+      <c r="S12" s="5">
+        <v>0.80469999999999997</v>
+      </c>
+      <c r="T12" s="5">
+        <v>0.83260000000000001</v>
+      </c>
+      <c r="U12" s="5">
+        <v>0.80620000000000003</v>
       </c>
       <c r="V12" s="8">
         <v>8.6243675760395905E-2</v>
@@ -2104,6 +2215,18 @@
       <c r="Q14" s="5">
         <v>0.5292</v>
       </c>
+      <c r="R14" s="17">
+        <v>0.86019999999999996</v>
+      </c>
+      <c r="S14" s="5">
+        <v>0.84309999999999996</v>
+      </c>
+      <c r="T14" s="5">
+        <v>0.80430000000000001</v>
+      </c>
+      <c r="U14" s="5">
+        <v>0.85409999999999997</v>
+      </c>
       <c r="V14" s="8">
         <v>8.6243675760395905E-2</v>
       </c>
@@ -2184,6 +2307,18 @@
       <c r="Q15" s="5">
         <v>0.53569999999999995</v>
       </c>
+      <c r="R15" s="17">
+        <v>0.84309999999999996</v>
+      </c>
+      <c r="S15" s="5">
+        <v>0.81020000000000003</v>
+      </c>
+      <c r="T15" s="5">
+        <v>0.82899999999999996</v>
+      </c>
+      <c r="U15" s="5">
+        <v>0.81899999999999995</v>
+      </c>
       <c r="V15" s="8">
         <v>8.6243675760395905E-2</v>
       </c>
@@ -2264,6 +2399,18 @@
       <c r="Q16" s="5">
         <v>0.54169999999999996</v>
       </c>
+      <c r="R16" s="17">
+        <v>0.86939999999999995</v>
+      </c>
+      <c r="S16" s="5">
+        <v>0.80069999999999997</v>
+      </c>
+      <c r="T16" s="5">
+        <v>0.80740000000000001</v>
+      </c>
+      <c r="U16" s="5">
+        <v>0.86199999999999999</v>
+      </c>
       <c r="V16" s="8">
         <v>8.6243675760395905E-2</v>
       </c>
@@ -2344,6 +2491,18 @@
       <c r="Q17" s="5">
         <v>0.57640000000000002</v>
       </c>
+      <c r="R17" s="17">
+        <v>0.85940000000000005</v>
+      </c>
+      <c r="S17" s="5">
+        <v>0.79239999999999999</v>
+      </c>
+      <c r="T17" s="5">
+        <v>0.82969999999999999</v>
+      </c>
+      <c r="U17" s="5">
+        <v>0.85419999999999996</v>
+      </c>
       <c r="V17" s="8">
         <v>8.6243675760395905E-2</v>
       </c>
@@ -2424,6 +2583,18 @@
       <c r="Q18" s="5">
         <v>0.58020000000000005</v>
       </c>
+      <c r="R18" s="17">
+        <v>0.85540000000000005</v>
+      </c>
+      <c r="S18" s="5">
+        <v>0.78820000000000001</v>
+      </c>
+      <c r="T18" s="5">
+        <v>0.84199999999999997</v>
+      </c>
+      <c r="U18" s="5">
+        <v>0.86180000000000001</v>
+      </c>
       <c r="V18" s="8">
         <v>8.6243675760395905E-2</v>
       </c>
@@ -2504,6 +2675,18 @@
       <c r="Q19" s="5">
         <v>0.53659999999999997</v>
       </c>
+      <c r="R19" s="17">
+        <v>0.87229999999999996</v>
+      </c>
+      <c r="S19" s="5">
+        <v>0.81659999999999999</v>
+      </c>
+      <c r="T19" s="5">
+        <v>0.8286</v>
+      </c>
+      <c r="U19" s="5">
+        <v>0.83540000000000003</v>
+      </c>
       <c r="V19" s="8">
         <v>8.6243675760395905E-2</v>
       </c>
@@ -2584,6 +2767,18 @@
       <c r="Q20" s="5">
         <v>0.57269999999999999</v>
       </c>
+      <c r="R20" s="17">
+        <v>0.87280000000000002</v>
+      </c>
+      <c r="S20" s="5">
+        <v>0.83889999999999998</v>
+      </c>
+      <c r="T20" s="5">
+        <v>0.86060000000000003</v>
+      </c>
+      <c r="U20" s="5">
+        <v>0.85260000000000002</v>
+      </c>
       <c r="V20" s="8">
         <v>8.6243675760395905E-2</v>
       </c>
@@ -2664,6 +2859,18 @@
       <c r="Q21" s="5">
         <v>0.54910000000000003</v>
       </c>
+      <c r="R21" s="17">
+        <v>0.85699999999999998</v>
+      </c>
+      <c r="S21" s="5">
+        <v>0.80130000000000001</v>
+      </c>
+      <c r="T21" s="5">
+        <v>0.82840000000000003</v>
+      </c>
+      <c r="U21" s="5">
+        <v>0.84109999999999996</v>
+      </c>
       <c r="V21" s="8">
         <v>8.6243675760395905E-2</v>
       </c>
@@ -2744,6 +2951,18 @@
       <c r="Q22" s="5">
         <v>0.58589999999999998</v>
       </c>
+      <c r="R22" s="17">
+        <v>0.85340000000000005</v>
+      </c>
+      <c r="S22" s="5">
+        <v>0.87070000000000003</v>
+      </c>
+      <c r="T22" s="5">
+        <v>0.83420000000000005</v>
+      </c>
+      <c r="U22" s="5">
+        <v>0.80620000000000003</v>
+      </c>
       <c r="V22" s="8">
         <v>8.6243675760395905E-2</v>
       </c>
@@ -2824,7 +3043,18 @@
       <c r="Q23" s="5">
         <v>0.60980000000000001</v>
       </c>
-      <c r="R23" s="17"/>
+      <c r="R23" s="17">
+        <v>0.88239999999999996</v>
+      </c>
+      <c r="S23" s="5">
+        <v>0.87280000000000002</v>
+      </c>
+      <c r="T23" s="5">
+        <v>0.88500000000000001</v>
+      </c>
+      <c r="U23" s="5">
+        <v>0.80420000000000003</v>
+      </c>
       <c r="V23" s="8">
         <v>8.6243675760395905E-2</v>
       </c>
@@ -2977,7 +3207,18 @@
       <c r="Q25" s="5">
         <v>0.60440000000000005</v>
       </c>
-      <c r="R25" s="17"/>
+      <c r="R25" s="17">
+        <v>0.8468</v>
+      </c>
+      <c r="S25" s="5">
+        <v>0.88580000000000003</v>
+      </c>
+      <c r="T25" s="5">
+        <v>0.82410000000000005</v>
+      </c>
+      <c r="U25" s="5">
+        <v>0.79920000000000002</v>
+      </c>
       <c r="V25" s="8">
         <v>8.6243675760395905E-2</v>
       </c>
@@ -3058,7 +3299,18 @@
       <c r="Q26" s="5">
         <v>0.58940000000000003</v>
       </c>
-      <c r="R26" s="17"/>
+      <c r="R26" s="17">
+        <v>0.86699999999999999</v>
+      </c>
+      <c r="S26" s="5">
+        <v>0.84460000000000002</v>
+      </c>
+      <c r="T26" s="5">
+        <v>0.84079999999999999</v>
+      </c>
+      <c r="U26" s="5">
+        <v>0.80420000000000003</v>
+      </c>
       <c r="V26" s="8">
         <v>8.6243675760395905E-2</v>
       </c>
@@ -3211,7 +3463,18 @@
       <c r="Q28" s="5">
         <v>0.58660000000000001</v>
       </c>
-      <c r="R28" s="17"/>
+      <c r="R28" s="17">
+        <v>0.87139999999999995</v>
+      </c>
+      <c r="S28" s="5">
+        <v>0.87809999999999999</v>
+      </c>
+      <c r="T28" s="5">
+        <v>0.82250000000000001</v>
+      </c>
+      <c r="U28" s="5">
+        <v>0.80610000000000004</v>
+      </c>
       <c r="V28" s="8">
         <v>8.6243675760395905E-2</v>
       </c>
@@ -3292,7 +3555,18 @@
       <c r="Q29" s="5">
         <v>0.5827</v>
       </c>
-      <c r="R29" s="17"/>
+      <c r="R29" s="17">
+        <v>0.85970000000000002</v>
+      </c>
+      <c r="S29" s="5">
+        <v>0.87429999999999997</v>
+      </c>
+      <c r="T29" s="5">
+        <v>0.8367</v>
+      </c>
+      <c r="U29" s="5">
+        <v>0.77980000000000005</v>
+      </c>
       <c r="V29" s="8">
         <v>8.6243675760395905E-2</v>
       </c>
@@ -3373,7 +3647,18 @@
       <c r="Q30" s="5">
         <v>0.61670000000000003</v>
       </c>
-      <c r="R30" s="17"/>
+      <c r="R30" s="17">
+        <v>0.8851</v>
+      </c>
+      <c r="S30" s="5">
+        <v>0.86980000000000002</v>
+      </c>
+      <c r="T30" s="5">
+        <v>0.86240000000000006</v>
+      </c>
+      <c r="U30" s="5">
+        <v>0.82540000000000002</v>
+      </c>
       <c r="V30" s="8">
         <v>8.6243675760395905E-2</v>
       </c>
@@ -3454,7 +3739,18 @@
       <c r="Q31" s="5">
         <v>0.58020000000000005</v>
       </c>
-      <c r="R31" s="17"/>
+      <c r="R31" s="17">
+        <v>0.85250000000000004</v>
+      </c>
+      <c r="S31" s="5">
+        <v>0.87160000000000004</v>
+      </c>
+      <c r="T31" s="5">
+        <v>0.82220000000000004</v>
+      </c>
+      <c r="U31" s="5">
+        <v>0.81630000000000003</v>
+      </c>
       <c r="V31" s="8">
         <v>8.6243675760395905E-2</v>
       </c>
